--- a/docs/downloads/04/tbl_other_chars_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_chars_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -622,12 +622,6 @@
           <t>Sexe</t>
         </is>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -686,12 +680,6 @@
           <t>Sexe</t>
         </is>
       </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -796,12 +784,6 @@
           <t>Sexe</t>
         </is>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1266,12 +1248,6 @@
           <t>Divorcé(e)</t>
         </is>
       </c>
-      <c r="D43">
-        <v>2</v>
-      </c>
-      <c r="E43">
-        <v>4.7</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1289,12 +1265,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <v>2.3</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1309,7 +1279,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D45">
@@ -1381,12 +1351,6 @@
           <t>Divorcé(e)</t>
         </is>
       </c>
-      <c r="D48">
-        <v>4</v>
-      </c>
-      <c r="E48">
-        <v>3.9</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1404,12 +1368,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D49">
-        <v>2</v>
-      </c>
-      <c r="E49">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1424,7 +1382,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D50">
@@ -1473,12 +1431,6 @@
           <t>Veuf(ve)</t>
         </is>
       </c>
-      <c r="D52">
-        <v>3</v>
-      </c>
-      <c r="E52">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1542,12 +1494,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D55">
-        <v>2</v>
-      </c>
-      <c r="E55">
-        <v>2.3</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1562,7 +1508,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D56">
@@ -1611,12 +1557,6 @@
           <t>Veuf(ve)</t>
         </is>
       </c>
-      <c r="D58">
-        <v>2</v>
-      </c>
-      <c r="E58">
-        <v>2.3</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1657,12 +1597,6 @@
           <t>Divorcé(e)</t>
         </is>
       </c>
-      <c r="D60">
-        <v>2</v>
-      </c>
-      <c r="E60">
-        <v>2.7</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1680,12 +1614,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D61">
-        <v>3</v>
-      </c>
-      <c r="E61">
-        <v>4</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1700,7 +1628,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D62">
@@ -1749,12 +1677,6 @@
           <t>Veuf(ve)</t>
         </is>
       </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>1.3</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1795,12 +1717,6 @@
           <t>Divorcé(e)</t>
         </is>
       </c>
-      <c r="D66">
-        <v>3</v>
-      </c>
-      <c r="E66">
-        <v>4.5</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1818,12 +1734,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1838,7 +1748,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D68">
@@ -1887,12 +1797,6 @@
           <t>Veuf(ve)</t>
         </is>
       </c>
-      <c r="D70">
-        <v>2</v>
-      </c>
-      <c r="E70">
-        <v>3</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1956,12 +1860,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D73">
-        <v>4</v>
-      </c>
-      <c r="E73">
-        <v>3.3</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1976,14 +1874,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D74">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E74">
-        <v>8.9</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="75">
@@ -1999,14 +1897,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="E75">
-        <v>5.7</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="76">
@@ -2022,20 +1920,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D76">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="E76">
-        <v>38.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2045,14 +1943,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>Célibataire</t>
         </is>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="E77">
-        <v>4.1</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="78">
@@ -2068,14 +1966,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D78">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="E78">
-        <v>41.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="79">
@@ -2091,14 +1989,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D79">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E79">
-        <v>4.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -2114,14 +2012,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D80">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E80">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -2137,14 +2035,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E81">
-        <v>3.6</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="82">
@@ -2160,20 +2058,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
-        </is>
-      </c>
-      <c r="D82">
-        <v>7</v>
-      </c>
-      <c r="E82">
-        <v>5.1</v>
+          <t>Veuf(ve)</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2183,20 +2075,20 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Célibataire</t>
         </is>
       </c>
       <c r="D83">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E83">
-        <v>36.5</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2206,14 +2098,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E84">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="85">
@@ -2229,14 +2121,8 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Célibataire</t>
-        </is>
-      </c>
-      <c r="D85">
-        <v>47</v>
-      </c>
-      <c r="E85">
-        <v>43.1</v>
+          <t>En concubinage</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -2252,14 +2138,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D86">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E86">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="87">
@@ -2275,14 +2161,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E87">
-        <v>0.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="88">
@@ -2298,20 +2184,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
-        </is>
-      </c>
-      <c r="D88">
-        <v>2</v>
-      </c>
-      <c r="E88">
-        <v>1.8</v>
+          <t>Veuf(ve)</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2321,20 +2201,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Célibataire</t>
         </is>
       </c>
       <c r="D89">
-        <v>4</v>
+        <v>284</v>
       </c>
       <c r="E89">
-        <v>3.7</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2344,20 +2224,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D90">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E90">
-        <v>43.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2367,14 +2247,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E91">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="92">
@@ -2390,14 +2270,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D92">
-        <v>284</v>
+        <v>111</v>
       </c>
       <c r="E92">
-        <v>38.2</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="93">
@@ -2413,14 +2293,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D93">
-        <v>37</v>
+        <v>272</v>
       </c>
       <c r="E93">
-        <v>5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="94">
@@ -2436,105 +2316,13 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D94">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E94">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Marié(e) civilement</t>
-        </is>
-      </c>
-      <c r="D95">
-        <v>93</v>
-      </c>
-      <c r="E95">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Marié(e) religieusement</t>
-        </is>
-      </c>
-      <c r="D96">
-        <v>18</v>
-      </c>
-      <c r="E96">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Marié(e) selon la tradition</t>
-        </is>
-      </c>
-      <c r="D97">
-        <v>272</v>
-      </c>
-      <c r="E97">
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D98">
-        <v>15</v>
-      </c>
-      <c r="E98">
         <v>2</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_other_chars_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_chars_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -476,7 +476,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -568,7 +568,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -672,7 +672,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -788,7 +788,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -834,7 +834,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -892,7 +892,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -952,7 +952,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -972,7 +972,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -992,7 +992,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1012,7 +1012,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1032,7 +1032,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1052,7 +1052,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1092,7 +1092,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1112,7 +1112,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1152,7 +1152,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1172,7 +1172,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1192,7 +1192,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1212,7 +1212,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1269,7 +1269,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1292,7 +1292,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1372,7 +1372,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1458,7 +1458,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1481,7 +1481,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1544,7 +1544,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1618,7 +1618,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1784,7 +1784,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1824,7 +1824,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1864,7 +1864,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1933,7 +1933,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1956,7 +1956,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1979,7 +1979,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2002,7 +2002,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2025,7 +2025,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2048,7 +2048,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2111,7 +2111,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2128,7 +2128,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2174,7 +2174,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2237,7 +2237,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2260,7 +2260,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2283,7 +2283,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2306,7 +2306,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">

--- a/docs/downloads/04/tbl_other_chars_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_chars_alaotra_tous.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D53">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E53">
-        <v>40.9</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="54">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
       <c r="E56">
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="57">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1538,7 +1538,7 @@
         <v>28</v>
       </c>
       <c r="E57">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="58">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="D71">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E71">
-        <v>33.3</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="72">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1841,7 +1841,7 @@
         <v>8</v>
       </c>
       <c r="E72">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="73">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1881,7 +1881,7 @@
         <v>18</v>
       </c>
       <c r="E74">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="75">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1904,7 +1904,7 @@
         <v>47</v>
       </c>
       <c r="E75">
-        <v>38.2</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="76">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1927,7 +1927,7 @@
         <v>5</v>
       </c>
       <c r="E76">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="77">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="D77">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E77">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="78">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="D79">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E79">
-        <v>8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="80">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2019,7 +2019,7 @@
         <v>12</v>
       </c>
       <c r="E80">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="81">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2042,7 +2042,7 @@
         <v>50</v>
       </c>
       <c r="E81">
-        <v>36.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="D89">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E89">
-        <v>38.2</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="90">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D91">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E91">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="92">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2277,7 +2277,7 @@
         <v>111</v>
       </c>
       <c r="E92">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="93">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2300,7 +2300,7 @@
         <v>272</v>
       </c>
       <c r="E93">
-        <v>36.6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Statut matrimonial</t>
+          <t>Statut matrimonial (12 ans et +)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
